--- a/OMOP Analysis/Results/Yearly/yearly_combined_bootstrap_summary_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Yearly/yearly_combined_bootstrap_summary_costs_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>521.264</v>
+        <v>709.951</v>
       </c>
       <c r="D2">
-        <v>10.468</v>
+        <v>20.774</v>
       </c>
       <c r="E2">
-        <v>3.235</v>
+        <v>4.558</v>
       </c>
       <c r="F2">
-        <v>0.102</v>
+        <v>0.144</v>
       </c>
       <c r="G2">
-        <v>515.051</v>
+        <v>701.127</v>
       </c>
       <c r="H2">
-        <v>527.734</v>
+        <v>718.994</v>
       </c>
       <c r="I2">
-        <v>515.152</v>
+        <v>701.0599999999999</v>
       </c>
       <c r="J2">
-        <v>527.688</v>
+        <v>718.798</v>
       </c>
       <c r="K2">
-        <v>514.9690000000001</v>
+        <v>701.213</v>
       </c>
       <c r="L2">
-        <v>527.504</v>
+        <v>718.952</v>
       </c>
     </row>
     <row r="3">
@@ -466,274 +466,114 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>438.946</v>
+        <v>609.2569999999999</v>
       </c>
       <c r="D3">
-        <v>14.533</v>
+        <v>28.683</v>
       </c>
       <c r="E3">
-        <v>3.812</v>
+        <v>5.356</v>
       </c>
       <c r="F3">
-        <v>0.121</v>
+        <v>0.169</v>
       </c>
       <c r="G3">
-        <v>431.581</v>
+        <v>599.001</v>
       </c>
       <c r="H3">
-        <v>446.525</v>
+        <v>619.995</v>
       </c>
       <c r="I3">
-        <v>431.778</v>
+        <v>598.766</v>
       </c>
       <c r="J3">
-        <v>446.596</v>
+        <v>620.0309999999999</v>
       </c>
       <c r="K3">
-        <v>431.403</v>
+        <v>598.724</v>
       </c>
       <c r="L3">
-        <v>446.221</v>
+        <v>619.9880000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>450.59</v>
+        <v>728.975</v>
       </c>
       <c r="D4">
-        <v>8.779999999999999</v>
+        <v>21.464</v>
       </c>
       <c r="E4">
-        <v>2.963</v>
+        <v>4.633</v>
       </c>
       <c r="F4">
-        <v>0.094</v>
+        <v>0.147</v>
       </c>
       <c r="G4">
-        <v>444.9</v>
+        <v>719.389</v>
       </c>
       <c r="H4">
-        <v>456.516</v>
+        <v>737.55</v>
       </c>
       <c r="I4">
-        <v>444.736</v>
+        <v>719.513</v>
       </c>
       <c r="J4">
-        <v>456.46</v>
+        <v>738.299</v>
       </c>
       <c r="K4">
-        <v>444.837</v>
+        <v>719.145</v>
       </c>
       <c r="L4">
-        <v>456.562</v>
+        <v>737.931</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>385.836</v>
+        <v>614.337</v>
       </c>
       <c r="D5">
-        <v>11.993</v>
+        <v>31.789</v>
       </c>
       <c r="E5">
-        <v>3.463</v>
+        <v>5.638</v>
       </c>
       <c r="F5">
-        <v>0.11</v>
+        <v>0.178</v>
       </c>
       <c r="G5">
-        <v>379.178</v>
+        <v>602.881</v>
       </c>
       <c r="H5">
-        <v>392.753</v>
+        <v>624.982</v>
       </c>
       <c r="I5">
-        <v>379.094</v>
+        <v>603.2670000000001</v>
       </c>
       <c r="J5">
-        <v>392.832</v>
+        <v>625.324</v>
       </c>
       <c r="K5">
-        <v>378.969</v>
+        <v>602.944</v>
       </c>
       <c r="L5">
-        <v>392.708</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>536.585</v>
-      </c>
-      <c r="D6">
-        <v>9.920999999999999</v>
-      </c>
-      <c r="E6">
-        <v>3.15</v>
-      </c>
-      <c r="F6">
-        <v>0.1</v>
-      </c>
-      <c r="G6">
-        <v>530.365</v>
-      </c>
-      <c r="H6">
-        <v>542.712</v>
-      </c>
-      <c r="I6">
-        <v>530.579</v>
-      </c>
-      <c r="J6">
-        <v>542.471</v>
-      </c>
-      <c r="K6">
-        <v>530.652</v>
-      </c>
-      <c r="L6">
-        <v>542.544</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>442.721</v>
-      </c>
-      <c r="D7">
-        <v>14.846</v>
-      </c>
-      <c r="E7">
-        <v>3.853</v>
-      </c>
-      <c r="F7">
-        <v>0.122</v>
-      </c>
-      <c r="G7">
-        <v>435.608</v>
-      </c>
-      <c r="H7">
-        <v>450.712</v>
-      </c>
-      <c r="I7">
-        <v>435.362</v>
-      </c>
-      <c r="J7">
-        <v>450.63</v>
-      </c>
-      <c r="K7">
-        <v>435.252</v>
-      </c>
-      <c r="L7">
-        <v>450.519</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>464.477</v>
-      </c>
-      <c r="D8">
-        <v>8.329000000000001</v>
-      </c>
-      <c r="E8">
-        <v>2.886</v>
-      </c>
-      <c r="F8">
-        <v>0.091</v>
-      </c>
-      <c r="G8">
-        <v>458.831</v>
-      </c>
-      <c r="H8">
-        <v>470.144</v>
-      </c>
-      <c r="I8">
-        <v>459.045</v>
-      </c>
-      <c r="J8">
-        <v>470.102</v>
-      </c>
-      <c r="K8">
-        <v>458.861</v>
-      </c>
-      <c r="L8">
-        <v>469.918</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>389.209</v>
-      </c>
-      <c r="D9">
-        <v>12.12</v>
-      </c>
-      <c r="E9">
-        <v>3.481</v>
-      </c>
-      <c r="F9">
-        <v>0.11</v>
-      </c>
-      <c r="G9">
-        <v>382.748</v>
-      </c>
-      <c r="H9">
-        <v>396.395</v>
-      </c>
-      <c r="I9">
-        <v>382.223</v>
-      </c>
-      <c r="J9">
-        <v>396.143</v>
-      </c>
-      <c r="K9">
-        <v>382.638</v>
-      </c>
-      <c r="L9">
-        <v>396.558</v>
+        <v>625.002</v>
       </c>
     </row>
   </sheetData>
